--- a/Results/Jump/DetectedAction/FindPrincipalComponents_PipelinePCA_Jump/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Jump/DetectedAction/FindPrincipalComponents_PipelinePCA_Jump/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -1090,40 +1090,40 @@
         <v>40</v>
       </c>
       <c r="B12" t="n">
-        <v>88.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>89.69841269841272</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D12" t="n">
-        <v>87.99999999999999</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>88.09427609427608</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G12" t="n">
-        <v>87.99999999999999</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H12" t="n">
-        <v>7.774602526460403</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I12" t="n">
-        <v>6.678070367607634</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J12" t="n">
-        <v>7.774602526460393</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8873012632302</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>7.470487456551007</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M12" t="n">
-        <v>7.774602526460393</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="13">
@@ -1254,40 +1254,40 @@
         <v>36</v>
       </c>
       <c r="B16" t="n">
-        <v>88.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>89.69841269841272</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D16" t="n">
-        <v>87.99999999999999</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>88.09427609427608</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G16" t="n">
-        <v>87.99999999999999</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H16" t="n">
-        <v>7.774602526460403</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I16" t="n">
-        <v>6.678070367607634</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J16" t="n">
-        <v>7.774602526460393</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8873012632302</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>7.470487456551007</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M16" t="n">
-        <v>7.774602526460393</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="17">
@@ -1459,40 +1459,40 @@
         <v>31</v>
       </c>
       <c r="B21" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C21" t="n">
-        <v>91.03174603174604</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D21" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E21" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F21" t="n">
-        <v>89.42760942760944</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G21" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H21" t="n">
-        <v>8.000000000000004</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>6.825396825396833</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J21" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L21" t="n">
-        <v>7.676767676767682</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M21" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="22">
@@ -1544,37 +1544,37 @@
         <v>89.33333333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>91.03174603174604</v>
+        <v>90.33333333333336</v>
       </c>
       <c r="D23" t="n">
-        <v>89.33333333333331</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="E23" t="n">
         <v>94.66666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>89.42760942760944</v>
+        <v>89.23905723905723</v>
       </c>
       <c r="G23" t="n">
-        <v>89.33333333333331</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>8.000000000000004</v>
+        <v>5.333333333333331</v>
       </c>
       <c r="I23" t="n">
-        <v>6.825396825396833</v>
+        <v>5.528824579833219</v>
       </c>
       <c r="J23" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333331</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="L23" t="n">
-        <v>7.676767676767682</v>
+        <v>5.38053459042612</v>
       </c>
       <c r="M23" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333331</v>
       </c>
     </row>
     <row r="24">
@@ -1746,40 +1746,40 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C28" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F28" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G28" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H28" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I28" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J28" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K28" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L28" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M28" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="29">
@@ -2197,40 +2197,40 @@
         <v>13</v>
       </c>
       <c r="B39" t="n">
-        <v>90.66666666666669</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>91.66666666666667</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D39" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="E39" t="n">
-        <v>95.33333333333334</v>
+        <v>96</v>
       </c>
       <c r="F39" t="n">
-        <v>90.57239057239057</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G39" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="H39" t="n">
-        <v>5.333333333333333</v>
+        <v>6.531972647421806</v>
       </c>
       <c r="I39" t="n">
-        <v>5.555555555555562</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J39" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K39" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710903</v>
       </c>
       <c r="L39" t="n">
-        <v>5.387205387205385</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M39" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="40">
@@ -4193,22 +4193,22 @@
         <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D56" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E56" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F56" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G56" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H56" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="57">
@@ -4713,22 +4713,22 @@
         <v>5</v>
       </c>
       <c r="C76" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D76" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E76" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F76" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G76" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H76" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="77">
@@ -5285,22 +5285,22 @@
         <v>2</v>
       </c>
       <c r="C98" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D98" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E98" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F98" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G98" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H98" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99">
@@ -5545,22 +5545,22 @@
         <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D108" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E108" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F108" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G108" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H108" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109">
@@ -5623,22 +5623,22 @@
         <v>5</v>
       </c>
       <c r="C111" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D111" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E111" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F111" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G111" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H111" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="112">
@@ -6247,22 +6247,22 @@
         <v>4</v>
       </c>
       <c r="C135" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D135" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E135" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F135" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G135" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H135" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="136">
@@ -7651,22 +7651,22 @@
         <v>3</v>
       </c>
       <c r="C189" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D189" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E189" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F189" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G189" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H189" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190">

--- a/Results/Jump/DetectedAction/FindPrincipalComponents_PipelinePCA_Jump/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Jump/DetectedAction/FindPrincipalComponents_PipelinePCA_Jump/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,991 +677,991 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>88.00000000000001</v>
+        <v>55.99999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>89.69841269841272</v>
+        <v>58.52645502645503</v>
       </c>
       <c r="D2" t="n">
-        <v>87.99999999999999</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
-        <v>88.09427609427608</v>
+        <v>54.18977318977318</v>
       </c>
       <c r="G2" t="n">
-        <v>87.99999999999999</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>7.774602526460403</v>
+        <v>13.72750685464933</v>
       </c>
       <c r="I2" t="n">
-        <v>6.678070367607634</v>
+        <v>14.93047163458518</v>
       </c>
       <c r="J2" t="n">
-        <v>7.774602526460393</v>
+        <v>13.72750685464933</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8873012632302</v>
+        <v>6.863753427324672</v>
       </c>
       <c r="L2" t="n">
-        <v>7.470487456551007</v>
+        <v>12.94822929938377</v>
       </c>
       <c r="M2" t="n">
-        <v>7.774602526460393</v>
+        <v>13.72750685464933</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00000000000001</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C3" t="n">
-        <v>89.69841269841272</v>
+        <v>70.50793650793652</v>
       </c>
       <c r="D3" t="n">
-        <v>87.99999999999999</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>88.09427609427608</v>
+        <v>64.46324046324045</v>
       </c>
       <c r="G3" t="n">
-        <v>87.99999999999999</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>7.774602526460403</v>
+        <v>7.302967433402213</v>
       </c>
       <c r="I3" t="n">
-        <v>6.678070367607634</v>
+        <v>10.10237967420967</v>
       </c>
       <c r="J3" t="n">
-        <v>7.774602526460393</v>
+        <v>7.302967433402217</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8873012632302</v>
+        <v>3.651483716701107</v>
       </c>
       <c r="L3" t="n">
-        <v>7.470487456551007</v>
+        <v>8.384492085764572</v>
       </c>
       <c r="M3" t="n">
-        <v>7.774602526460393</v>
+        <v>7.302967433402217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>88.00000000000001</v>
+        <v>73.33333333333331</v>
       </c>
       <c r="C4" t="n">
-        <v>89.69841269841272</v>
+        <v>74.8174603174603</v>
       </c>
       <c r="D4" t="n">
-        <v>87.99999999999999</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>88.09427609427608</v>
+        <v>72.2965552965553</v>
       </c>
       <c r="G4" t="n">
-        <v>87.99999999999999</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>7.774602526460403</v>
+        <v>5.962847939999443</v>
       </c>
       <c r="I4" t="n">
-        <v>6.678070367607634</v>
+        <v>7.058657164609862</v>
       </c>
       <c r="J4" t="n">
-        <v>7.774602526460393</v>
+        <v>5.962847939999443</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8873012632302</v>
+        <v>2.981423969999719</v>
       </c>
       <c r="L4" t="n">
-        <v>7.470487456551007</v>
+        <v>6.474502834595724</v>
       </c>
       <c r="M4" t="n">
-        <v>7.774602526460393</v>
+        <v>5.962847939999443</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>88.00000000000001</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>89.69841269841272</v>
+        <v>80.2063492063492</v>
       </c>
       <c r="D5" t="n">
-        <v>87.99999999999999</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>88.09427609427608</v>
+        <v>77.85666185666186</v>
       </c>
       <c r="G5" t="n">
-        <v>87.99999999999999</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="H5" t="n">
+        <v>7.774602526460404</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.526153275025271</v>
+      </c>
+      <c r="J5" t="n">
         <v>7.774602526460403</v>
       </c>
-      <c r="I5" t="n">
-        <v>6.678070367607634</v>
-      </c>
-      <c r="J5" t="n">
-        <v>7.774602526460393</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.8873012632302</v>
+        <v>3.887301263230194</v>
       </c>
       <c r="L5" t="n">
-        <v>7.470487456551007</v>
+        <v>8.547844160485763</v>
       </c>
       <c r="M5" t="n">
-        <v>7.774602526460393</v>
+        <v>7.774602526460403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>88.00000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>89.69841269841272</v>
+        <v>88.55555555555554</v>
       </c>
       <c r="D6" t="n">
-        <v>87.99999999999999</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>88.09427609427608</v>
+        <v>87.93265993265994</v>
       </c>
       <c r="G6" t="n">
-        <v>87.99999999999999</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>7.774602526460403</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I6" t="n">
-        <v>6.678070367607634</v>
+        <v>6.320650068145732</v>
       </c>
       <c r="J6" t="n">
-        <v>7.774602526460393</v>
+        <v>6.531972647421809</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8873012632302</v>
+        <v>3.265986323710905</v>
       </c>
       <c r="L6" t="n">
-        <v>7.470487456551007</v>
+        <v>6.587139162026051</v>
       </c>
       <c r="M6" t="n">
-        <v>7.774602526460393</v>
+        <v>6.531972647421809</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>88.00000000000001</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>89.69841269841272</v>
+        <v>92.44444444444446</v>
       </c>
       <c r="D7" t="n">
-        <v>87.99999999999999</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>88.09427609427608</v>
+        <v>91.97306397306397</v>
       </c>
       <c r="G7" t="n">
-        <v>87.99999999999999</v>
+        <v>92</v>
       </c>
       <c r="H7" t="n">
-        <v>7.774602526460403</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="I7" t="n">
-        <v>6.678070367607634</v>
+        <v>5.13520889257393</v>
       </c>
       <c r="J7" t="n">
-        <v>7.774602526460393</v>
+        <v>4.988876515698586</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8873012632302</v>
+        <v>2.494438257849299</v>
       </c>
       <c r="L7" t="n">
-        <v>7.470487456551007</v>
+        <v>4.981781589757502</v>
       </c>
       <c r="M7" t="n">
-        <v>7.774602526460393</v>
+        <v>4.988876515698586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>88.00000000000001</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>89.69841269841272</v>
+        <v>92.44444444444446</v>
       </c>
       <c r="D8" t="n">
-        <v>87.99999999999999</v>
+        <v>92</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>88.09427609427608</v>
+        <v>91.97306397306397</v>
       </c>
       <c r="G8" t="n">
-        <v>87.99999999999999</v>
+        <v>92</v>
       </c>
       <c r="H8" t="n">
-        <v>7.774602526460403</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="I8" t="n">
-        <v>6.678070367607634</v>
+        <v>5.13520889257393</v>
       </c>
       <c r="J8" t="n">
-        <v>7.774602526460393</v>
+        <v>4.988876515698586</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8873012632302</v>
+        <v>2.494438257849299</v>
       </c>
       <c r="L8" t="n">
-        <v>7.470487456551007</v>
+        <v>4.981781589757502</v>
       </c>
       <c r="M8" t="n">
-        <v>7.774602526460393</v>
+        <v>4.988876515698586</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>88.00000000000001</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>89.69841269841272</v>
+        <v>94</v>
       </c>
       <c r="D9" t="n">
-        <v>87.99999999999999</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>96.66666666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>88.09427609427608</v>
+        <v>93.2929292929293</v>
       </c>
       <c r="G9" t="n">
-        <v>87.99999999999999</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>7.774602526460403</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="I9" t="n">
-        <v>6.678070367607634</v>
+        <v>4.251361437713108</v>
       </c>
       <c r="J9" t="n">
-        <v>7.774602526460393</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8873012632302</v>
+        <v>2.108185106778923</v>
       </c>
       <c r="L9" t="n">
-        <v>7.470487456551007</v>
+        <v>4.216499270970933</v>
       </c>
       <c r="M9" t="n">
-        <v>7.774602526460393</v>
+        <v>4.216370213557838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>89.33333333333333</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>91.03174603174604</v>
+        <v>94</v>
       </c>
       <c r="D10" t="n">
-        <v>89.33333333333331</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>94.66666666666667</v>
+        <v>96.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>89.42760942760944</v>
+        <v>93.2929292929293</v>
       </c>
       <c r="G10" t="n">
-        <v>89.33333333333331</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>8.000000000000004</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="I10" t="n">
-        <v>6.825396825396833</v>
+        <v>4.251361437713108</v>
       </c>
       <c r="J10" t="n">
-        <v>7.999999999999995</v>
+        <v>4.216370213557838</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>2.108185106778923</v>
       </c>
       <c r="L10" t="n">
-        <v>7.676767676767682</v>
+        <v>4.216499270970933</v>
       </c>
       <c r="M10" t="n">
-        <v>7.999999999999995</v>
+        <v>4.216370213557838</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>89.33333333333333</v>
+        <v>92</v>
       </c>
       <c r="C11" t="n">
-        <v>91.03174603174604</v>
+        <v>92.66666666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="E11" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>89.42760942760944</v>
+        <v>91.95959595959596</v>
       </c>
       <c r="G11" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="H11" t="n">
-        <v>8.000000000000004</v>
+        <v>4.988876515698588</v>
       </c>
       <c r="I11" t="n">
-        <v>6.825396825396833</v>
+        <v>4.898979485566358</v>
       </c>
       <c r="J11" t="n">
-        <v>7.999999999999995</v>
+        <v>4.988876515698586</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>2.494438257849299</v>
       </c>
       <c r="L11" t="n">
-        <v>7.676767676767682</v>
+        <v>4.996179201987482</v>
       </c>
       <c r="M11" t="n">
-        <v>7.999999999999995</v>
+        <v>4.988876515698586</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="C12" t="n">
-        <v>91.03174603174604</v>
+        <v>91.44444444444446</v>
       </c>
       <c r="D12" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>89.42760942760944</v>
+        <v>90.58585858585857</v>
       </c>
       <c r="G12" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>8.000000000000004</v>
+        <v>6.798692684790378</v>
       </c>
       <c r="I12" t="n">
-        <v>6.825396825396833</v>
+        <v>6.681465057054631</v>
       </c>
       <c r="J12" t="n">
-        <v>7.999999999999995</v>
+        <v>6.798692684790381</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.39934634239519</v>
       </c>
       <c r="L12" t="n">
-        <v>7.676767676767682</v>
+        <v>6.859490774020786</v>
       </c>
       <c r="M12" t="n">
-        <v>7.999999999999995</v>
+        <v>6.798692684790381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="C13" t="n">
-        <v>91.03174603174604</v>
+        <v>91.44444444444446</v>
       </c>
       <c r="D13" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E13" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>89.42760942760944</v>
+        <v>90.58585858585857</v>
       </c>
       <c r="G13" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H13" t="n">
-        <v>8.000000000000004</v>
+        <v>6.798692684790378</v>
       </c>
       <c r="I13" t="n">
-        <v>6.825396825396833</v>
+        <v>6.681465057054631</v>
       </c>
       <c r="J13" t="n">
-        <v>7.999999999999995</v>
+        <v>6.798692684790381</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.39934634239519</v>
       </c>
       <c r="L13" t="n">
-        <v>7.676767676767682</v>
+        <v>6.859490774020786</v>
       </c>
       <c r="M13" t="n">
-        <v>7.999999999999995</v>
+        <v>6.798692684790381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C14" t="n">
-        <v>91.03174603174604</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E14" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>89.42760942760944</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G14" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>8.000000000000004</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>6.825396825396833</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J14" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L14" t="n">
-        <v>7.676767676767682</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M14" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C15" t="n">
-        <v>91.03174603174604</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E15" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>89.42760942760944</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G15" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H15" t="n">
-        <v>8.000000000000004</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>6.825396825396833</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J15" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L15" t="n">
-        <v>7.676767676767682</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M15" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>89.33333333333333</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>91.03174603174604</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D16" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="E16" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="F16" t="n">
-        <v>89.42760942760944</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G16" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="H16" t="n">
-        <v>8.000000000000004</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I16" t="n">
-        <v>6.825396825396833</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J16" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L16" t="n">
-        <v>7.676767676767682</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M16" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>89.33333333333333</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>91.03174603174604</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D17" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="E17" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
-        <v>89.42760942760944</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G17" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="H17" t="n">
-        <v>8.000000000000004</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I17" t="n">
-        <v>6.825396825396833</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J17" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L17" t="n">
-        <v>7.676767676767682</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M17" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C18" t="n">
-        <v>91.03174603174604</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E18" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>89.42760942760944</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G18" t="n">
-        <v>89.33333333333331</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H18" t="n">
-        <v>8.000000000000004</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>6.825396825396833</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J18" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L18" t="n">
-        <v>7.676767676767682</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M18" t="n">
-        <v>7.999999999999995</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>89.33333333333333</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>91.03174603174604</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D19" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="E19" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>89.42760942760944</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G19" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="H19" t="n">
-        <v>8.000000000000004</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I19" t="n">
-        <v>6.825396825396833</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J19" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L19" t="n">
-        <v>7.676767676767682</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M19" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>89.33333333333333</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>91.03174603174604</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D20" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="E20" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>89.42760942760944</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G20" t="n">
-        <v>89.33333333333331</v>
+        <v>92</v>
       </c>
       <c r="H20" t="n">
-        <v>8.000000000000004</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I20" t="n">
-        <v>6.825396825396833</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J20" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L20" t="n">
-        <v>7.676767676767682</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M20" t="n">
-        <v>7.999999999999995</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>90.66666666666669</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>91.66666666666667</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D21" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="E21" t="n">
-        <v>95.33333333333334</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
-        <v>90.57239057239057</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G21" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="H21" t="n">
-        <v>5.333333333333333</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I21" t="n">
-        <v>5.555555555555562</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J21" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K21" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L21" t="n">
-        <v>5.387205387205385</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M21" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>90.66666666666669</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>91.66666666666667</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D22" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="E22" t="n">
-        <v>95.33333333333334</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>90.57239057239057</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G22" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="H22" t="n">
-        <v>5.333333333333333</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I22" t="n">
-        <v>5.555555555555562</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J22" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K22" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L22" t="n">
-        <v>5.387205387205385</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M22" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>89.33333333333333</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>90.33333333333336</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D23" t="n">
-        <v>89.33333333333333</v>
+        <v>92</v>
       </c>
       <c r="E23" t="n">
-        <v>94.66666666666667</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
-        <v>89.23905723905723</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G23" t="n">
-        <v>89.33333333333333</v>
+        <v>92</v>
       </c>
       <c r="H23" t="n">
-        <v>5.333333333333331</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I23" t="n">
-        <v>5.528824579833219</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J23" t="n">
-        <v>5.333333333333331</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K23" t="n">
-        <v>2.666666666666667</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L23" t="n">
-        <v>5.38053459042612</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M23" t="n">
-        <v>5.333333333333331</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>90.66666666666669</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>91.66666666666667</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D24" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="E24" t="n">
-        <v>95.33333333333334</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>90.57239057239057</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G24" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="H24" t="n">
-        <v>5.333333333333333</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I24" t="n">
-        <v>5.555555555555562</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J24" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K24" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L24" t="n">
-        <v>5.387205387205385</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M24" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>90.66666666666669</v>
+        <v>92.00000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>91.66666666666667</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="D25" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="E25" t="n">
-        <v>95.33333333333334</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>90.57239057239057</v>
+        <v>91.91919191919192</v>
       </c>
       <c r="G25" t="n">
-        <v>90.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="H25" t="n">
-        <v>5.333333333333333</v>
+        <v>6.531972647421807</v>
       </c>
       <c r="I25" t="n">
-        <v>5.555555555555562</v>
+        <v>6.478835438717005</v>
       </c>
       <c r="J25" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
       <c r="K25" t="n">
-        <v>2.666666666666666</v>
+        <v>3.265986323710904</v>
       </c>
       <c r="L25" t="n">
-        <v>5.387205387205385</v>
+        <v>6.597952169112936</v>
       </c>
       <c r="M25" t="n">
-        <v>5.333333333333332</v>
+        <v>6.53197264742181</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="n">
         <v>90.66666666666669</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="n">
         <v>90.66666666666669</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B28" t="n">
         <v>90.66666666666669</v>
@@ -1784,945 +1784,904 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C29" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E29" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G29" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J29" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K29" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L29" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M29" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>92.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>92.77777777777779</v>
+        <v>90.33333333333336</v>
       </c>
       <c r="D30" t="n">
-        <v>92</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="E30" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F30" t="n">
-        <v>91.91919191919192</v>
+        <v>89.23905723905723</v>
       </c>
       <c r="G30" t="n">
-        <v>92</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="H30" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333331</v>
       </c>
       <c r="I30" t="n">
-        <v>6.478835438717005</v>
+        <v>5.528824579833219</v>
       </c>
       <c r="J30" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333331</v>
       </c>
       <c r="K30" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="L30" t="n">
-        <v>6.597952169112936</v>
+        <v>5.38053459042612</v>
       </c>
       <c r="M30" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333331</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C31" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E31" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F31" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G31" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H31" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I31" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J31" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K31" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L31" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M31" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C32" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E32" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F32" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G32" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I32" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J32" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K32" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L32" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M32" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C33" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E33" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F33" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G33" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H33" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I33" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J33" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K33" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L33" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M33" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>92.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C34" t="n">
-        <v>92.77777777777779</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D34" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E34" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F34" t="n">
-        <v>91.91919191919192</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G34" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H34" t="n">
-        <v>6.531972647421807</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I34" t="n">
-        <v>6.478835438717005</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J34" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K34" t="n">
-        <v>3.265986323710904</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>6.597952169112936</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M34" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>90.66666666666669</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C35" t="n">
-        <v>91.66666666666667</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D35" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E35" t="n">
-        <v>95.33333333333334</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F35" t="n">
-        <v>90.57239057239057</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G35" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H35" t="n">
-        <v>5.333333333333333</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I35" t="n">
-        <v>5.555555555555562</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J35" t="n">
-        <v>5.333333333333332</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K35" t="n">
-        <v>2.666666666666666</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>5.387205387205385</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M35" t="n">
-        <v>5.333333333333332</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>92.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>92.77777777777779</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D36" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E36" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F36" t="n">
-        <v>91.91919191919192</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G36" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H36" t="n">
-        <v>6.531972647421807</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I36" t="n">
-        <v>6.478835438717005</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J36" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K36" t="n">
-        <v>3.265986323710904</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
-        <v>6.597952169112936</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M36" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>92.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C37" t="n">
-        <v>92.77777777777779</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E37" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>91.91919191919192</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G37" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H37" t="n">
-        <v>6.531972647421807</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I37" t="n">
-        <v>6.478835438717005</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J37" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K37" t="n">
-        <v>3.265986323710904</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
-        <v>6.597952169112936</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M37" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>90.66666666666669</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C38" t="n">
-        <v>91.66666666666667</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D38" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E38" t="n">
-        <v>95.33333333333334</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>90.57239057239057</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G38" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H38" t="n">
-        <v>5.333333333333333</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I38" t="n">
-        <v>5.555555555555562</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J38" t="n">
-        <v>5.333333333333332</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K38" t="n">
-        <v>2.666666666666666</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>5.387205387205385</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M38" t="n">
-        <v>5.333333333333332</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>92.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C39" t="n">
-        <v>92.77777777777779</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D39" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E39" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F39" t="n">
-        <v>91.91919191919192</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G39" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H39" t="n">
-        <v>6.531972647421806</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I39" t="n">
-        <v>6.478835438717005</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J39" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K39" t="n">
-        <v>3.265986323710903</v>
+        <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>6.597952169112936</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M39" t="n">
-        <v>6.53197264742181</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C40" t="n">
-        <v>91.44444444444446</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D40" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E40" t="n">
-        <v>95.33333333333334</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>90.58585858585857</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G40" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H40" t="n">
-        <v>6.798692684790378</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I40" t="n">
-        <v>6.681465057054631</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J40" t="n">
-        <v>6.798692684790381</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K40" t="n">
-        <v>3.39934634239519</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>6.859490774020786</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M40" t="n">
-        <v>6.798692684790381</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C41" t="n">
-        <v>91.44444444444446</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D41" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E41" t="n">
-        <v>95.33333333333334</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>90.58585858585857</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G41" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H41" t="n">
-        <v>6.798692684790378</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I41" t="n">
-        <v>6.681465057054631</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J41" t="n">
-        <v>6.798692684790381</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K41" t="n">
-        <v>3.39934634239519</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>6.859490774020786</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M41" t="n">
-        <v>6.798692684790381</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>92</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C42" t="n">
-        <v>92.66666666666667</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D42" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E42" t="n">
-        <v>96</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F42" t="n">
-        <v>91.95959595959596</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G42" t="n">
-        <v>92</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H42" t="n">
-        <v>4.988876515698588</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I42" t="n">
-        <v>4.898979485566358</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J42" t="n">
-        <v>4.988876515698586</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K42" t="n">
-        <v>2.494438257849299</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
-        <v>4.996179201987482</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M42" t="n">
-        <v>4.988876515698586</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>93.33333333333333</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C43" t="n">
-        <v>94</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D43" t="n">
-        <v>93.33333333333333</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E43" t="n">
-        <v>96.66666666666666</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F43" t="n">
-        <v>93.2929292929293</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G43" t="n">
-        <v>93.33333333333333</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H43" t="n">
-        <v>4.216370213557838</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I43" t="n">
-        <v>4.251361437713108</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J43" t="n">
-        <v>4.216370213557838</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K43" t="n">
-        <v>2.108185106778923</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
-        <v>4.216499270970933</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M43" t="n">
-        <v>4.216370213557838</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>93.33333333333333</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C44" t="n">
+        <v>89.69841269841272</v>
+      </c>
+      <c r="D44" t="n">
+        <v>87.99999999999999</v>
+      </c>
+      <c r="E44" t="n">
         <v>94</v>
       </c>
-      <c r="D44" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="E44" t="n">
-        <v>96.66666666666666</v>
-      </c>
       <c r="F44" t="n">
-        <v>93.2929292929293</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G44" t="n">
-        <v>93.33333333333333</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>4.216370213557838</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I44" t="n">
-        <v>4.251361437713108</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J44" t="n">
-        <v>4.216370213557838</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K44" t="n">
-        <v>2.108185106778923</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L44" t="n">
-        <v>4.216499270970933</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M44" t="n">
-        <v>4.216370213557838</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>92</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>92.44444444444446</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D45" t="n">
-        <v>92</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F45" t="n">
-        <v>91.97306397306397</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G45" t="n">
-        <v>92</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>4.988876515698588</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I45" t="n">
-        <v>5.13520889257393</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J45" t="n">
-        <v>4.988876515698586</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K45" t="n">
-        <v>2.494438257849299</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L45" t="n">
-        <v>4.981781589757502</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M45" t="n">
-        <v>4.988876515698586</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>92</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>92.44444444444446</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D46" t="n">
-        <v>92</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F46" t="n">
-        <v>91.97306397306397</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G46" t="n">
-        <v>92</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>4.988876515698588</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I46" t="n">
-        <v>5.13520889257393</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J46" t="n">
-        <v>4.988876515698586</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K46" t="n">
-        <v>2.494438257849299</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L46" t="n">
-        <v>4.981781589757502</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M46" t="n">
-        <v>4.988876515698586</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B47" t="n">
         <v>88.00000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>88.55555555555554</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D47" t="n">
-        <v>88.00000000000001</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E47" t="n">
         <v>94</v>
       </c>
       <c r="F47" t="n">
-        <v>87.93265993265994</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G47" t="n">
-        <v>88.00000000000001</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>6.531972647421807</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I47" t="n">
-        <v>6.320650068145732</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J47" t="n">
-        <v>6.531972647421809</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K47" t="n">
-        <v>3.265986323710905</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L47" t="n">
-        <v>6.587139162026051</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M47" t="n">
-        <v>6.531972647421809</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>78.66666666666667</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>80.2063492063492</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D48" t="n">
-        <v>78.66666666666667</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>89.33333333333333</v>
+        <v>94</v>
       </c>
       <c r="F48" t="n">
-        <v>77.85666185666186</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G48" t="n">
-        <v>78.66666666666667</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>7.774602526460404</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I48" t="n">
-        <v>7.526153275025271</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J48" t="n">
-        <v>7.774602526460403</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K48" t="n">
-        <v>3.887301263230194</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L48" t="n">
-        <v>8.547844160485763</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M48" t="n">
-        <v>7.774602526460403</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>73.33333333333331</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>74.8174603174603</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D49" t="n">
-        <v>73.33333333333333</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66666666666666</v>
+        <v>94</v>
       </c>
       <c r="F49" t="n">
-        <v>72.2965552965553</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G49" t="n">
-        <v>73.33333333333333</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>5.962847939999443</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I49" t="n">
-        <v>7.058657164609862</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J49" t="n">
-        <v>5.962847939999443</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K49" t="n">
-        <v>2.981423969999719</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L49" t="n">
-        <v>6.474502834595724</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M49" t="n">
-        <v>5.962847939999443</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>66.66666666666666</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>70.50793650793652</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D50" t="n">
-        <v>66.66666666666666</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>83.33333333333334</v>
+        <v>94</v>
       </c>
       <c r="F50" t="n">
-        <v>64.46324046324045</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G50" t="n">
-        <v>66.66666666666666</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>7.302967433402213</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I50" t="n">
-        <v>10.10237967420967</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J50" t="n">
-        <v>7.302967433402217</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K50" t="n">
-        <v>3.651483716701107</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L50" t="n">
-        <v>8.384492085764572</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M50" t="n">
-        <v>7.302967433402217</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" t="n">
-        <v>55.99999999999999</v>
-      </c>
-      <c r="C51" t="n">
-        <v>58.52645502645503</v>
-      </c>
-      <c r="D51" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="E51" t="n">
-        <v>78</v>
-      </c>
-      <c r="F51" t="n">
-        <v>54.18977318977318</v>
-      </c>
-      <c r="G51" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="H51" t="n">
-        <v>13.72750685464933</v>
-      </c>
-      <c r="I51" t="n">
-        <v>14.93047163458518</v>
-      </c>
-      <c r="J51" t="n">
-        <v>13.72750685464933</v>
-      </c>
-      <c r="K51" t="n">
-        <v>6.863753427324672</v>
-      </c>
-      <c r="L51" t="n">
-        <v>12.94822929938377</v>
-      </c>
-      <c r="M51" t="n">
-        <v>13.72750685464933</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2783,163 +2742,163 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D2" t="n">
-        <v>94.44444444444446</v>
+        <v>84.92063492063492</v>
       </c>
       <c r="E2" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>96.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>93.26599326599326</v>
+        <v>77.12842712842712</v>
       </c>
       <c r="H2" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.33333333333333</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>77.38095238095238</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="E3" t="n">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="F3" t="n">
         <v>73.33333333333334</v>
       </c>
-      <c r="F3" t="n">
-        <v>86.66666666666667</v>
-      </c>
       <c r="G3" t="n">
-        <v>74.07407407407406</v>
+        <v>43.38624338624338</v>
       </c>
       <c r="H3" t="n">
-        <v>73.33333333333334</v>
+        <v>46.66666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>93.33333333333333</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>94.44444444444446</v>
+        <v>41.11111111111111</v>
       </c>
       <c r="E4" t="n">
-        <v>93.33333333333333</v>
+        <v>40.00000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>96.66666666666667</v>
+        <v>69.99999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>93.26599326599326</v>
+        <v>40.26936026936027</v>
       </c>
       <c r="H4" t="n">
-        <v>93.33333333333333</v>
+        <v>40.00000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>94.44444444444446</v>
+        <v>60.95238095238095</v>
       </c>
       <c r="E5" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>96.66666666666667</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>93.26599326599326</v>
+        <v>54.99999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>86.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>87.77777777777777</v>
+        <v>57.50000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>86.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>93.33333333333333</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>86.5993265993266</v>
+        <v>55.16483516483516</v>
       </c>
       <c r="H6" t="n">
-        <v>86.66666666666667</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>94.44444444444446</v>
+        <v>74.60317460317461</v>
       </c>
       <c r="E7" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>96.66666666666667</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>93.26599326599326</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="H7" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -2948,16 +2907,16 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>77.38095238095238</v>
+        <v>80.15873015873018</v>
       </c>
       <c r="E8" t="n">
         <v>73.33333333333334</v>
       </c>
       <c r="F8" t="n">
-        <v>86.66666666666667</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="G8" t="n">
-        <v>74.07407407407406</v>
+        <v>71.57287157287156</v>
       </c>
       <c r="H8" t="n">
         <v>73.33333333333334</v>
@@ -2965,449 +2924,449 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D9" t="n">
-        <v>94.44444444444446</v>
+        <v>51.38888888888889</v>
       </c>
       <c r="E9" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>96.66666666666667</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>93.26599326599326</v>
+        <v>49.71509971509971</v>
       </c>
       <c r="H9" t="n">
-        <v>93.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D10" t="n">
-        <v>94.44444444444446</v>
+        <v>70</v>
       </c>
       <c r="E10" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>96.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>93.26599326599326</v>
+        <v>67.81144781144781</v>
       </c>
       <c r="H10" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D11" t="n">
-        <v>87.77777777777777</v>
+        <v>76.38888888888889</v>
       </c>
       <c r="E11" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F11" t="n">
-        <v>93.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>86.5993265993266</v>
+        <v>60.994560994561</v>
       </c>
       <c r="H11" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>94.44444444444446</v>
+        <v>76.38888888888889</v>
       </c>
       <c r="E12" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>96.66666666666667</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>93.26599326599326</v>
+        <v>71.93732193732193</v>
       </c>
       <c r="H12" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>73.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D13" t="n">
-        <v>77.38095238095238</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="E13" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F13" t="n">
-        <v>86.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>74.07407407407406</v>
+        <v>65.15151515151516</v>
       </c>
       <c r="H13" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D14" t="n">
-        <v>94.44444444444446</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="E14" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>96.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>93.26599326599326</v>
+        <v>65.15151515151516</v>
       </c>
       <c r="H14" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>94.44444444444446</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E15" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>96.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G15" t="n">
-        <v>93.26599326599326</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H15" t="n">
-        <v>93.33333333333333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>86.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="D16" t="n">
-        <v>87.77777777777777</v>
+        <v>83.80952380952381</v>
       </c>
       <c r="E16" t="n">
-        <v>86.66666666666667</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>93.33333333333333</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>86.5993265993266</v>
+        <v>79.44444444444446</v>
       </c>
       <c r="H16" t="n">
-        <v>86.66666666666667</v>
+        <v>80.00000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D17" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E17" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H17" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D18" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E18" t="n">
-        <v>73.33333333333334</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797979</v>
       </c>
       <c r="H18" t="n">
-        <v>73.33333333333334</v>
+        <v>80.00000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D19" t="n">
-        <v>94.44444444444446</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="E19" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F19" t="n">
-        <v>96.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>93.26599326599326</v>
+        <v>65.15151515151516</v>
       </c>
       <c r="H19" t="n">
-        <v>93.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>94.44444444444446</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E20" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>93.26599326599326</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
         <v>5</v>
       </c>
       <c r="C21" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>79.36507936507937</v>
+      </c>
+      <c r="E21" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="F21" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="D21" t="n">
-        <v>87.77777777777777</v>
-      </c>
-      <c r="E21" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="F21" t="n">
-        <v>93.33333333333333</v>
-      </c>
       <c r="G21" t="n">
-        <v>86.5993265993266</v>
+        <v>71.06782106782106</v>
       </c>
       <c r="H21" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D22" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E22" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H22" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D23" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E23" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G23" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H23" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E24" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H24" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D25" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E25" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
         <v>5</v>
@@ -3416,7 +3375,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="D26" t="n">
-        <v>87.77777777777777</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E26" t="n">
         <v>86.66666666666667</v>
@@ -3425,7 +3384,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>86.5993265993266</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="H26" t="n">
         <v>86.66666666666667</v>
@@ -3433,7 +3392,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -3459,33 +3418,33 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>77.38095238095238</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F28" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G28" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="G28" t="n">
-        <v>74.07407407407406</v>
-      </c>
       <c r="H28" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
         <v>3</v>
@@ -3511,33 +3470,33 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D30" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E30" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
@@ -3546,7 +3505,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>87.77777777777777</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E31" t="n">
         <v>86.66666666666667</v>
@@ -3555,7 +3514,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="G31" t="n">
-        <v>86.5993265993266</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="H31" t="n">
         <v>86.66666666666667</v>
@@ -3563,7 +3522,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -3589,33 +3548,33 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>77.38095238095238</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E33" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F33" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G33" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="G33" t="n">
-        <v>74.07407407407406</v>
-      </c>
       <c r="H33" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
@@ -3641,33 +3600,33 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D35" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F35" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B36" t="n">
         <v>5</v>
@@ -3676,7 +3635,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="D36" t="n">
-        <v>87.77777777777777</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E36" t="n">
         <v>86.66666666666667</v>
@@ -3685,7 +3644,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>86.5993265993266</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="H36" t="n">
         <v>86.66666666666667</v>
@@ -3693,7 +3652,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
@@ -3719,33 +3678,33 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D38" t="n">
-        <v>77.38095238095238</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E38" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F38" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G38" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="G38" t="n">
-        <v>74.07407407407406</v>
-      </c>
       <c r="H38" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
@@ -3771,59 +3730,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D40" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E40" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F40" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D41" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E41" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F41" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H41" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
@@ -3849,33 +3808,33 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D43" t="n">
-        <v>77.38095238095238</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E43" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F43" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G43" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="G43" t="n">
-        <v>74.07407407407406</v>
-      </c>
       <c r="H43" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B44" t="n">
         <v>3</v>
@@ -3901,33 +3860,33 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D45" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E45" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B46" t="n">
         <v>5</v>
@@ -3953,7 +3912,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>1</v>
@@ -3979,33 +3938,33 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D48" t="n">
-        <v>77.38095238095238</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="E48" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F48" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G48" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="G48" t="n">
-        <v>74.07407407407406</v>
-      </c>
       <c r="H48" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B49" t="n">
         <v>3</v>
@@ -4031,59 +3990,59 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D50" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E50" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F50" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H50" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B51" t="n">
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D51" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E51" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F51" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H51" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B52" t="n">
         <v>1</v>
@@ -4109,33 +4068,33 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D53" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E53" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F53" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G53" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H53" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B54" t="n">
         <v>3</v>
@@ -4161,59 +4120,59 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E55" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F55" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
         <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D56" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E56" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F56" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G56" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H56" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B57" t="n">
         <v>1</v>
@@ -4239,33 +4198,33 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D58" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E58" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F58" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G58" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H58" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B59" t="n">
         <v>3</v>
@@ -4291,59 +4250,59 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D60" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E60" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H60" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B61" t="n">
         <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D61" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E61" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F61" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H61" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B62" t="n">
         <v>1</v>
@@ -4369,33 +4328,33 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D63" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E63" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F63" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G63" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H63" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B64" t="n">
         <v>3</v>
@@ -4421,7 +4380,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B65" t="n">
         <v>4</v>
@@ -4447,7 +4406,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B66" t="n">
         <v>5</v>
@@ -4473,7 +4432,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B67" t="n">
         <v>1</v>
@@ -4499,33 +4458,33 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D68" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E68" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F68" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G68" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H68" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B69" t="n">
         <v>3</v>
@@ -4551,7 +4510,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B70" t="n">
         <v>4</v>
@@ -4577,7 +4536,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B71" t="n">
         <v>5</v>
@@ -4603,7 +4562,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B72" t="n">
         <v>1</v>
@@ -4629,33 +4588,33 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D73" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E73" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F73" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G73" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H73" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B74" t="n">
         <v>3</v>
@@ -4681,33 +4640,33 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B75" t="n">
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D75" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F75" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B76" t="n">
         <v>5</v>
@@ -4733,7 +4692,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B77" t="n">
         <v>1</v>
@@ -4759,33 +4718,33 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E78" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F78" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G78" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H78" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B79" t="n">
         <v>3</v>
@@ -4811,33 +4770,33 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E80" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F80" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H80" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B81" t="n">
         <v>5</v>
@@ -4863,7 +4822,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B82" t="n">
         <v>1</v>
@@ -4889,33 +4848,33 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D83" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E83" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F83" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G83" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H83" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B84" t="n">
         <v>3</v>
@@ -4941,7 +4900,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B85" t="n">
         <v>4</v>
@@ -4967,7 +4926,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B86" t="n">
         <v>5</v>
@@ -4993,7 +4952,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B87" t="n">
         <v>1</v>
@@ -5019,33 +4978,33 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B88" t="n">
         <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E88" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F88" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G88" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H88" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B89" t="n">
         <v>3</v>
@@ -5071,33 +5030,33 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B90" t="n">
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D90" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E90" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F90" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B91" t="n">
         <v>5</v>
@@ -5123,7 +5082,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B92" t="n">
         <v>1</v>
@@ -5149,33 +5108,33 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B93" t="n">
         <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D93" t="n">
-        <v>77.38095238095238</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E93" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F93" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G93" t="n">
-        <v>74.07407407407406</v>
+        <v>79.79797979797981</v>
       </c>
       <c r="H93" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B94" t="n">
         <v>3</v>
@@ -5201,33 +5160,33 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E95" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H95" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B96" t="n">
         <v>5</v>
@@ -5253,7 +5212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B97" t="n">
         <v>1</v>
@@ -5279,7 +5238,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B98" t="n">
         <v>2</v>
@@ -5305,7 +5264,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B99" t="n">
         <v>3</v>
@@ -5331,33 +5290,33 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B100" t="n">
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D100" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E100" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G100" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H100" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B101" t="n">
         <v>5</v>
@@ -5383,7 +5342,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B102" t="n">
         <v>1</v>
@@ -5409,7 +5368,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B103" t="n">
         <v>2</v>
@@ -5435,7 +5394,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B104" t="n">
         <v>3</v>
@@ -5461,33 +5420,33 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D105" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E105" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F105" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G105" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H105" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B106" t="n">
         <v>5</v>
@@ -5513,7 +5472,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -5539,7 +5498,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B108" t="n">
         <v>2</v>
@@ -5565,7 +5524,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B109" t="n">
         <v>3</v>
@@ -5591,59 +5550,59 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B110" t="n">
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D110" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E110" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F110" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H110" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B111" t="n">
         <v>5</v>
       </c>
       <c r="C111" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D111" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E111" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F111" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G111" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H111" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B112" t="n">
         <v>1</v>
@@ -5669,7 +5628,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B113" t="n">
         <v>2</v>
@@ -5695,7 +5654,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B114" t="n">
         <v>3</v>
@@ -5721,33 +5680,33 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B115" t="n">
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D115" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E115" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F115" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G115" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H115" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B116" t="n">
         <v>5</v>
@@ -5773,7 +5732,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B117" t="n">
         <v>1</v>
@@ -5799,7 +5758,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B118" t="n">
         <v>2</v>
@@ -5825,7 +5784,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B119" t="n">
         <v>3</v>
@@ -5851,33 +5810,33 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B120" t="n">
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D120" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E120" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F120" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G120" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H120" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B121" t="n">
         <v>5</v>
@@ -5903,7 +5862,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B122" t="n">
         <v>1</v>
@@ -5929,7 +5888,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B123" t="n">
         <v>2</v>
@@ -5955,7 +5914,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B124" t="n">
         <v>3</v>
@@ -5981,7 +5940,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B125" t="n">
         <v>4</v>
@@ -6007,7 +5966,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B126" t="n">
         <v>5</v>
@@ -6033,7 +5992,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B127" t="n">
         <v>1</v>
@@ -6059,7 +6018,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B128" t="n">
         <v>2</v>
@@ -6085,7 +6044,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B129" t="n">
         <v>3</v>
@@ -6111,7 +6070,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B130" t="n">
         <v>4</v>
@@ -6137,7 +6096,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B131" t="n">
         <v>5</v>
@@ -6163,7 +6122,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B132" t="n">
         <v>1</v>
@@ -6189,7 +6148,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B133" t="n">
         <v>2</v>
@@ -6215,7 +6174,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B134" t="n">
         <v>3</v>
@@ -6241,7 +6200,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B135" t="n">
         <v>4</v>
@@ -6267,7 +6226,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B136" t="n">
         <v>5</v>
@@ -6293,7 +6252,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B137" t="n">
         <v>1</v>
@@ -6319,7 +6278,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B138" t="n">
         <v>2</v>
@@ -6345,7 +6304,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B139" t="n">
         <v>3</v>
@@ -6371,33 +6330,33 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B140" t="n">
         <v>4</v>
       </c>
       <c r="C140" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D140" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E140" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F140" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G140" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H140" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B141" t="n">
         <v>5</v>
@@ -6423,7 +6382,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B142" t="n">
         <v>1</v>
@@ -6449,7 +6408,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B143" t="n">
         <v>2</v>
@@ -6475,7 +6434,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B144" t="n">
         <v>3</v>
@@ -6501,59 +6460,59 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B145" t="n">
         <v>4</v>
       </c>
       <c r="C145" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D145" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E145" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F145" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G145" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H145" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B146" t="n">
         <v>5</v>
       </c>
       <c r="C146" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D146" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E146" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F146" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G146" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H146" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B147" t="n">
         <v>1</v>
@@ -6579,7 +6538,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B148" t="n">
         <v>2</v>
@@ -6605,7 +6564,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B149" t="n">
         <v>3</v>
@@ -6631,33 +6590,33 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B150" t="n">
         <v>4</v>
       </c>
       <c r="C150" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D150" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E150" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F150" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G150" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H150" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B151" t="n">
         <v>5</v>
@@ -6683,7 +6642,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B152" t="n">
         <v>1</v>
@@ -6709,7 +6668,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B153" t="n">
         <v>2</v>
@@ -6735,7 +6694,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B154" t="n">
         <v>3</v>
@@ -6761,33 +6720,33 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B155" t="n">
         <v>4</v>
       </c>
       <c r="C155" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D155" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E155" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F155" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G155" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H155" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B156" t="n">
         <v>5</v>
@@ -6813,7 +6772,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B157" t="n">
         <v>1</v>
@@ -6839,7 +6798,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B158" t="n">
         <v>2</v>
@@ -6865,7 +6824,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B159" t="n">
         <v>3</v>
@@ -6891,33 +6850,33 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B160" t="n">
         <v>4</v>
       </c>
       <c r="C160" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D160" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E160" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F160" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G160" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H160" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B161" t="n">
         <v>5</v>
@@ -6943,7 +6902,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B162" t="n">
         <v>1</v>
@@ -6969,33 +6928,33 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B163" t="n">
         <v>2</v>
       </c>
       <c r="C163" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D163" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E163" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F163" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G163" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H163" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B164" t="n">
         <v>3</v>
@@ -7021,33 +6980,33 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B165" t="n">
         <v>4</v>
       </c>
       <c r="C165" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D165" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E165" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F165" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G165" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H165" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B166" t="n">
         <v>5</v>
@@ -7073,7 +7032,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B167" t="n">
         <v>1</v>
@@ -7099,33 +7058,33 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B168" t="n">
         <v>2</v>
       </c>
       <c r="C168" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D168" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E168" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F168" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G168" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H168" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B169" t="n">
         <v>3</v>
@@ -7151,7 +7110,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B170" t="n">
         <v>4</v>
@@ -7177,7 +7136,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B171" t="n">
         <v>5</v>
@@ -7203,7 +7162,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B172" t="n">
         <v>1</v>
@@ -7229,33 +7188,33 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B173" t="n">
         <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D173" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E173" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F173" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G173" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H173" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B174" t="n">
         <v>3</v>
@@ -7281,33 +7240,33 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B175" t="n">
         <v>4</v>
       </c>
       <c r="C175" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D175" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E175" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F175" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G175" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H175" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B176" t="n">
         <v>5</v>
@@ -7333,7 +7292,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B177" t="n">
         <v>1</v>
@@ -7359,33 +7318,33 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B178" t="n">
         <v>2</v>
       </c>
       <c r="C178" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D178" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E178" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F178" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G178" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H178" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B179" t="n">
         <v>3</v>
@@ -7411,33 +7370,33 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B180" t="n">
         <v>4</v>
       </c>
       <c r="C180" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D180" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E180" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F180" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G180" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H180" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B181" t="n">
         <v>5</v>
@@ -7463,7 +7422,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B182" t="n">
         <v>1</v>
@@ -7489,33 +7448,33 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B183" t="n">
         <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D183" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E183" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F183" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G183" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H183" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B184" t="n">
         <v>3</v>
@@ -7541,7 +7500,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B185" t="n">
         <v>4</v>
@@ -7567,7 +7526,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B186" t="n">
         <v>5</v>
@@ -7593,7 +7552,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B187" t="n">
         <v>1</v>
@@ -7619,59 +7578,59 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B188" t="n">
         <v>2</v>
       </c>
       <c r="C188" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D188" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E188" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F188" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G188" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H188" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B189" t="n">
         <v>3</v>
       </c>
       <c r="C189" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D189" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E189" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F189" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G189" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H189" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B190" t="n">
         <v>4</v>
@@ -7697,7 +7656,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B191" t="n">
         <v>5</v>
@@ -7723,7 +7682,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B192" t="n">
         <v>1</v>
@@ -7749,33 +7708,33 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B193" t="n">
         <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D193" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E193" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F193" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G193" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H193" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B194" t="n">
         <v>3</v>
@@ -7801,59 +7760,59 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B195" t="n">
         <v>4</v>
       </c>
       <c r="C195" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D195" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E195" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F195" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G195" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H195" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B196" t="n">
         <v>5</v>
       </c>
       <c r="C196" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D196" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E196" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F196" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G196" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H196" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B197" t="n">
         <v>1</v>
@@ -7879,33 +7838,33 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B198" t="n">
         <v>2</v>
       </c>
       <c r="C198" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D198" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E198" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F198" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G198" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H198" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B199" t="n">
         <v>3</v>
@@ -7931,59 +7890,59 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B200" t="n">
         <v>4</v>
       </c>
       <c r="C200" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D200" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E200" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F200" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G200" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H200" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B201" t="n">
         <v>5</v>
       </c>
       <c r="C201" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D201" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E201" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F201" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G201" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H201" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B202" t="n">
         <v>1</v>
@@ -8009,33 +7968,33 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B203" t="n">
         <v>2</v>
       </c>
       <c r="C203" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D203" t="n">
+        <v>77.38095238095238</v>
+      </c>
+      <c r="E203" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="F203" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="D203" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="E203" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="F203" t="n">
-        <v>93.33333333333333</v>
-      </c>
       <c r="G203" t="n">
-        <v>86.66666666666667</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H203" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B204" t="n">
         <v>3</v>
@@ -8061,59 +8020,59 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B205" t="n">
         <v>4</v>
       </c>
       <c r="C205" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D205" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E205" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F205" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G205" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H205" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B206" t="n">
         <v>5</v>
       </c>
       <c r="C206" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D206" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E206" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F206" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G206" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H206" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B207" t="n">
         <v>1</v>
@@ -8139,33 +8098,33 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B208" t="n">
         <v>2</v>
       </c>
       <c r="C208" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D208" t="n">
+        <v>77.38095238095238</v>
+      </c>
+      <c r="E208" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="F208" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="D208" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="E208" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="F208" t="n">
-        <v>93.33333333333333</v>
-      </c>
       <c r="G208" t="n">
-        <v>86.66666666666667</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H208" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B209" t="n">
         <v>3</v>
@@ -8191,33 +8150,33 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B210" t="n">
         <v>4</v>
       </c>
       <c r="C210" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D210" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E210" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F210" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G210" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H210" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B211" t="n">
         <v>5</v>
@@ -8243,7 +8202,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B212" t="n">
         <v>1</v>
@@ -8269,33 +8228,33 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B213" t="n">
         <v>2</v>
       </c>
       <c r="C213" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D213" t="n">
+        <v>77.38095238095238</v>
+      </c>
+      <c r="E213" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="F213" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="D213" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="E213" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="F213" t="n">
-        <v>93.33333333333333</v>
-      </c>
       <c r="G213" t="n">
-        <v>86.66666666666667</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H213" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B214" t="n">
         <v>3</v>
@@ -8321,59 +8280,59 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B215" t="n">
         <v>4</v>
       </c>
       <c r="C215" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D215" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E215" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F215" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G215" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H215" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B216" t="n">
         <v>5</v>
       </c>
       <c r="C216" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D216" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E216" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F216" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G216" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H216" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B217" t="n">
         <v>1</v>
@@ -8399,33 +8358,33 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B218" t="n">
         <v>2</v>
       </c>
       <c r="C218" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D218" t="n">
+        <v>77.38095238095238</v>
+      </c>
+      <c r="E218" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="F218" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="D218" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="E218" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="F218" t="n">
-        <v>93.33333333333333</v>
-      </c>
       <c r="G218" t="n">
-        <v>86.66666666666667</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H218" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B219" t="n">
         <v>3</v>
@@ -8451,33 +8410,33 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B220" t="n">
         <v>4</v>
       </c>
       <c r="C220" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D220" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E220" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F220" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G220" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H220" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B221" t="n">
         <v>5</v>
@@ -8486,7 +8445,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="D221" t="n">
-        <v>86.66666666666667</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E221" t="n">
         <v>86.66666666666667</v>
@@ -8495,7 +8454,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="G221" t="n">
-        <v>86.66666666666667</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H221" t="n">
         <v>86.66666666666667</v>
@@ -8503,7 +8462,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B222" t="n">
         <v>1</v>
@@ -8529,33 +8488,33 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B223" t="n">
         <v>2</v>
       </c>
       <c r="C223" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D223" t="n">
+        <v>77.38095238095238</v>
+      </c>
+      <c r="E223" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="F223" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="D223" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="E223" t="n">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="F223" t="n">
-        <v>93.33333333333333</v>
-      </c>
       <c r="G223" t="n">
-        <v>86.66666666666667</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H223" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B224" t="n">
         <v>3</v>
@@ -8581,33 +8540,33 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B225" t="n">
         <v>4</v>
       </c>
       <c r="C225" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D225" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E225" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F225" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G225" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H225" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B226" t="n">
         <v>5</v>
@@ -8616,7 +8575,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="D226" t="n">
-        <v>86.66666666666667</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E226" t="n">
         <v>86.66666666666667</v>
@@ -8625,7 +8584,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="G226" t="n">
-        <v>86.66666666666667</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H226" t="n">
         <v>86.66666666666667</v>
@@ -8633,111 +8592,111 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B227" t="n">
         <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D227" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E227" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F227" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G227" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H227" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B228" t="n">
         <v>2</v>
       </c>
       <c r="C228" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D228" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E228" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F228" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G228" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H228" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B229" t="n">
         <v>3</v>
       </c>
       <c r="C229" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D229" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E229" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F229" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G229" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H229" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B230" t="n">
         <v>4</v>
       </c>
       <c r="C230" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D230" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E230" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F230" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G230" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H230" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B231" t="n">
         <v>5</v>
@@ -8746,7 +8705,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="D231" t="n">
-        <v>86.66666666666667</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E231" t="n">
         <v>86.66666666666667</v>
@@ -8755,7 +8714,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="G231" t="n">
-        <v>86.66666666666667</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H231" t="n">
         <v>86.66666666666667</v>
@@ -8763,293 +8722,293 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B232" t="n">
         <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D232" t="n">
-        <v>87.77777777777777</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E232" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F232" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G232" t="n">
-        <v>86.5993265993266</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H232" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B233" t="n">
         <v>2</v>
       </c>
       <c r="C233" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D233" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E233" t="n">
-        <v>80.00000000000001</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F233" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G233" t="n">
-        <v>79.79797979797979</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H233" t="n">
-        <v>80.00000000000001</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B234" t="n">
         <v>3</v>
       </c>
       <c r="C234" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D234" t="n">
-        <v>66.66666666666666</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E234" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F234" t="n">
-        <v>83.33333333333334</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G234" t="n">
-        <v>65.15151515151516</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H234" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B235" t="n">
         <v>4</v>
       </c>
       <c r="C235" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D235" t="n">
-        <v>86.66666666666667</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E235" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F235" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G235" t="n">
-        <v>86.66666666666667</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H235" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B236" t="n">
         <v>5</v>
       </c>
       <c r="C236" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D236" t="n">
-        <v>79.36507936507937</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E236" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F236" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="G236" t="n">
+        <v>86.5993265993266</v>
+      </c>
+      <c r="H236" t="n">
         <v>86.66666666666667</v>
-      </c>
-      <c r="G236" t="n">
-        <v>71.06782106782106</v>
-      </c>
-      <c r="H236" t="n">
-        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B237" t="n">
         <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>73.33333333333333</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D237" t="n">
-        <v>76.38888888888889</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E237" t="n">
-        <v>73.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F237" t="n">
-        <v>86.66666666666666</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G237" t="n">
-        <v>71.93732193732193</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H237" t="n">
-        <v>73.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B238" t="n">
         <v>2</v>
       </c>
       <c r="C238" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D238" t="n">
-        <v>66.66666666666666</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E238" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F238" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G238" t="n">
-        <v>65.15151515151516</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H238" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B239" t="n">
         <v>3</v>
       </c>
       <c r="C239" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D239" t="n">
-        <v>66.66666666666666</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E239" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F239" t="n">
-        <v>83.33333333333334</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G239" t="n">
-        <v>65.15151515151516</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H239" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B240" t="n">
         <v>4</v>
       </c>
       <c r="C240" t="n">
-        <v>80</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D240" t="n">
-        <v>80.55555555555554</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E240" t="n">
-        <v>80</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F240" t="n">
-        <v>90</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G240" t="n">
-        <v>79.79797979797981</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H240" t="n">
-        <v>80</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B241" t="n">
         <v>5</v>
       </c>
       <c r="C241" t="n">
-        <v>80</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D241" t="n">
-        <v>83.80952380952381</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E241" t="n">
-        <v>80.00000000000001</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F241" t="n">
-        <v>90</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G241" t="n">
-        <v>79.44444444444446</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H241" t="n">
-        <v>80.00000000000001</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B242" t="n">
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>73.33333333333333</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D242" t="n">
-        <v>74.60317460317461</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E242" t="n">
-        <v>73.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F242" t="n">
-        <v>86.66666666666666</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G242" t="n">
-        <v>72.22222222222221</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H242" t="n">
-        <v>73.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B243" t="n">
         <v>2</v>
@@ -9058,16 +9017,16 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D243" t="n">
-        <v>80.15873015873018</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E243" t="n">
         <v>73.33333333333334</v>
       </c>
       <c r="F243" t="n">
-        <v>86.66666666666666</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G243" t="n">
-        <v>71.57287157287156</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H243" t="n">
         <v>73.33333333333334</v>
@@ -9075,210 +9034,80 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B244" t="n">
         <v>3</v>
       </c>
       <c r="C244" t="n">
-        <v>53.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D244" t="n">
-        <v>51.38888888888889</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E244" t="n">
-        <v>53.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F244" t="n">
-        <v>76.66666666666666</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G244" t="n">
-        <v>49.71509971509971</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H244" t="n">
-        <v>53.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B245" t="n">
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D245" t="n">
-        <v>70</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E245" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F245" t="n">
-        <v>83.33333333333334</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G245" t="n">
-        <v>67.81144781144781</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H245" t="n">
-        <v>66.66666666666666</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B246" t="n">
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>66.66666666666666</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D246" t="n">
-        <v>76.38888888888889</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E246" t="n">
-        <v>66.66666666666666</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F246" t="n">
-        <v>83.33333333333334</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G246" t="n">
-        <v>60.994560994561</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H246" t="n">
-        <v>66.66666666666666</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>1</v>
-      </c>
-      <c r="B247" t="n">
-        <v>1</v>
-      </c>
-      <c r="C247" t="n">
-        <v>80</v>
-      </c>
-      <c r="D247" t="n">
-        <v>84.92063492063492</v>
-      </c>
-      <c r="E247" t="n">
-        <v>80</v>
-      </c>
-      <c r="F247" t="n">
-        <v>90</v>
-      </c>
-      <c r="G247" t="n">
-        <v>77.12842712842712</v>
-      </c>
-      <c r="H247" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>1</v>
-      </c>
-      <c r="B248" t="n">
-        <v>2</v>
-      </c>
-      <c r="C248" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="D248" t="n">
-        <v>48.14814814814815</v>
-      </c>
-      <c r="E248" t="n">
-        <v>46.66666666666667</v>
-      </c>
-      <c r="F248" t="n">
-        <v>73.33333333333334</v>
-      </c>
-      <c r="G248" t="n">
-        <v>43.38624338624338</v>
-      </c>
-      <c r="H248" t="n">
-        <v>46.66666666666667</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>1</v>
-      </c>
-      <c r="B249" t="n">
-        <v>3</v>
-      </c>
-      <c r="C249" t="n">
-        <v>40</v>
-      </c>
-      <c r="D249" t="n">
-        <v>41.11111111111111</v>
-      </c>
-      <c r="E249" t="n">
-        <v>40.00000000000001</v>
-      </c>
-      <c r="F249" t="n">
-        <v>69.99999999999999</v>
-      </c>
-      <c r="G249" t="n">
-        <v>40.26936026936027</v>
-      </c>
-      <c r="H249" t="n">
-        <v>40.00000000000001</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>1</v>
-      </c>
-      <c r="B250" t="n">
-        <v>4</v>
-      </c>
-      <c r="C250" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="D250" t="n">
-        <v>60.95238095238095</v>
-      </c>
-      <c r="E250" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="F250" t="n">
-        <v>76.66666666666666</v>
-      </c>
-      <c r="G250" t="n">
-        <v>54.99999999999999</v>
-      </c>
-      <c r="H250" t="n">
-        <v>53.33333333333334</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>1</v>
-      </c>
-      <c r="B251" t="n">
-        <v>5</v>
-      </c>
-      <c r="C251" t="n">
-        <v>60</v>
-      </c>
-      <c r="D251" t="n">
-        <v>57.50000000000001</v>
-      </c>
-      <c r="E251" t="n">
-        <v>60</v>
-      </c>
-      <c r="F251" t="n">
-        <v>80.00000000000001</v>
-      </c>
-      <c r="G251" t="n">
-        <v>55.16483516483516</v>
-      </c>
-      <c r="H251" t="n">
-        <v>60</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9319,7 +9148,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>93.2929292929293</v>
@@ -9332,7 +9161,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>93.33333333333333</v>
@@ -9345,7 +9174,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>93.33333333333333</v>

--- a/Results/Jump/DetectedAction/FindPrincipalComponents_PipelinePCA_Jump/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Jump/DetectedAction/FindPrincipalComponents_PipelinePCA_Jump/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,10 +585,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Show Accuracy Threshold</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accuracy Threshold (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Highlight Acceptable Accuracy</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Master Path</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>/Users/mohammad/University/Bachelor Project/Final/DetectedActionData/Jump/Master Features/MASTER_Features_Jump.xlsx</t>
         </is>
@@ -1295,40 +1325,40 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C17" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D17" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G17" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H17" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J17" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K17" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L17" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M17" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="18">
@@ -1582,40 +1612,40 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>92.00000000000001</v>
+        <v>90.66666666666669</v>
       </c>
       <c r="C24" t="n">
-        <v>92.77777777777779</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F24" t="n">
-        <v>91.91919191919192</v>
+        <v>90.57239057239057</v>
       </c>
       <c r="G24" t="n">
-        <v>92</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H24" t="n">
-        <v>6.531972647421807</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>6.478835438717005</v>
+        <v>5.555555555555562</v>
       </c>
       <c r="J24" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
       <c r="K24" t="n">
-        <v>3.265986323710904</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="L24" t="n">
-        <v>6.597952169112936</v>
+        <v>5.387205387205385</v>
       </c>
       <c r="M24" t="n">
-        <v>6.53197264742181</v>
+        <v>5.333333333333332</v>
       </c>
     </row>
     <row r="25">
@@ -1951,40 +1981,40 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>90.66666666666669</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C33" t="n">
-        <v>91.66666666666667</v>
+        <v>91.03174603174604</v>
       </c>
       <c r="D33" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="E33" t="n">
-        <v>95.33333333333334</v>
+        <v>94.66666666666667</v>
       </c>
       <c r="F33" t="n">
-        <v>90.57239057239057</v>
+        <v>89.42760942760944</v>
       </c>
       <c r="G33" t="n">
-        <v>90.66666666666666</v>
+        <v>89.33333333333331</v>
       </c>
       <c r="H33" t="n">
-        <v>5.333333333333333</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="I33" t="n">
-        <v>5.555555555555562</v>
+        <v>6.825396825396833</v>
       </c>
       <c r="J33" t="n">
-        <v>5.333333333333332</v>
+        <v>7.999999999999995</v>
       </c>
       <c r="K33" t="n">
-        <v>2.666666666666666</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
-        <v>5.387205387205385</v>
+        <v>7.676767676767682</v>
       </c>
       <c r="M33" t="n">
-        <v>5.333333333333332</v>
+        <v>7.999999999999995</v>
       </c>
     </row>
     <row r="34">
@@ -2279,40 +2309,40 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>89.33333333333333</v>
+        <v>88.00000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>91.03174603174604</v>
+        <v>89.69841269841272</v>
       </c>
       <c r="D41" t="n">
-        <v>89.33333333333331</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>94.66666666666667</v>
+        <v>94</v>
       </c>
       <c r="F41" t="n">
-        <v>89.42760942760944</v>
+        <v>88.09427609427608</v>
       </c>
       <c r="G41" t="n">
-        <v>89.33333333333331</v>
+        <v>87.99999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>8.000000000000004</v>
+        <v>7.774602526460403</v>
       </c>
       <c r="I41" t="n">
-        <v>6.825396825396833</v>
+        <v>6.678070367607634</v>
       </c>
       <c r="J41" t="n">
-        <v>7.999999999999995</v>
+        <v>7.774602526460393</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>3.8873012632302</v>
       </c>
       <c r="L41" t="n">
-        <v>7.676767676767682</v>
+        <v>7.470487456551007</v>
       </c>
       <c r="M41" t="n">
-        <v>7.999999999999995</v>
+        <v>7.774602526460393</v>
       </c>
     </row>
     <row r="42">
@@ -4776,22 +4806,22 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D80" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F80" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G80" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="81">
@@ -5686,22 +5716,22 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D115" t="n">
-        <v>100</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G115" t="n">
-        <v>100</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H115" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="116">
@@ -6804,22 +6834,22 @@
         <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D158" t="n">
-        <v>80.55555555555554</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="E158" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F158" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G158" t="n">
-        <v>79.79797979797981</v>
+        <v>74.07407407407406</v>
       </c>
       <c r="H158" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
     </row>
     <row r="159">
@@ -7922,22 +7952,22 @@
         <v>5</v>
       </c>
       <c r="C201" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D201" t="n">
-        <v>94.44444444444446</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E201" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F201" t="n">
-        <v>96.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G201" t="n">
-        <v>93.26599326599326</v>
+        <v>86.5993265993266</v>
       </c>
       <c r="H201" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
     </row>
     <row r="202">
